--- a/artfynd/A 16893-2023 artfynd.xlsx
+++ b/artfynd/A 16893-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 16893-2023 artfynd.xlsx
+++ b/artfynd/A 16893-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>606971</v>
+        <v>69568233</v>
       </c>
       <c r="B2" t="n">
-        <v>104401</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>103034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1562</v>
+        <v>1400</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stortimjan</t>
+          <t>Flikros</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Thymus pulegioides</t>
+          <t>Rosa tomentella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Léman</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,19 +710,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rommareberget, Bl</t>
+          <t>Romareberget, V om, Bl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503010.7350847609</v>
+        <v>502817</v>
       </c>
       <c r="R2" t="n">
-        <v>6228251.222853553</v>
+        <v>6228346</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,34 +752,14 @@
           <t>Åryd</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>K-Khn-0070</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-07-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2008-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>eftersök på gammal lokal</t>
+          <t>2006-07-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,18 +771,266 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>skogbryn/bergkant</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Åke Widgren</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Åke Widgren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>69568234</v>
+      </c>
+      <c r="B3" t="n">
+        <v>103034</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Flikros</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Rosa tomentella</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Léman</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Romareberget, SV om, Bl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>502856</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6228078</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Karlshamn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Åryd</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2006-07-20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2006-07-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ytterligare 1 ex 50 m åt norr</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>skogbryn/bergkant</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Biologiska Museet, Lunds Universitet</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Åke Widgren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Åke Widgren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>606971</v>
+      </c>
+      <c r="B4" t="n">
+        <v>107514</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1562</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stortimjan</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Thymus pulegioides</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rommareberget, Bl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>503011</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6228251</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlshamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Åryd</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>K-Khn-0070</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2008-01-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2008-12-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>eftersök på gammal lokal</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>K-län Floraväktarna</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Kjell Pettersson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 16893-2023 artfynd.xlsx
+++ b/artfynd/A 16893-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69568233</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69568234</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,8 +1050,18 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/606971</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>